--- a/artifacts/soma.xlsx
+++ b/artifacts/soma.xlsx
@@ -25,36 +25,40 @@
     <sheet name="QuantityValue" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Unit" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="NamedEntity" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ExposureCondition" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="CellularSystem" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="CellLine" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="CellCultureConditions" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="CellCultureMedium" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="MediumSupplement" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="QuantityRange" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="CiliaryFunctionAssay" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="CiliaryFunctionOutput" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="ASLAssay" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="ASLOutput" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="MucociliaryClearanceAssay" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="MucociliaryClearanceOutput" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="OxidativeStressAssay" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="OxidativeStressOutput" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="CFTRFunctionAssay" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="CFTRFunctionOutput" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="EGFRSignalingAssay" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="EGFRSignalingOutput" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="GobletCellAssay" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="GobletCellOutput" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="BALFSputumAssay" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="BALFSputumOutput" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="LungFunctionAssay" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="LungFunctionOutput" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="FoxJExpressionAssay" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="FoxJExpressionOutput" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="GeneExpressionAssay" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="GeneExpressionOutput" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="Container" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="CellTypeReference" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SpeciesReference" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ChemicalEntityReference" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="AnatomicalEntityReference" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="ExposureCondition" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="CellularSystem" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="CellLine" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="CellCultureConditions" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="CellCultureMedium" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="MediumSupplement" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="QuantityRange" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="CiliaryFunctionAssay" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="CiliaryFunctionOutput" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ASLAssay" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ASLOutput" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="MucociliaryClearanceAssay" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="MucociliaryClearanceOutput" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="OxidativeStressAssay" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="OxidativeStressOutput" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="CFTRFunctionAssay" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="CFTRFunctionOutput" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="EGFRSignalingAssay" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="EGFRSignalingOutput" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="GobletCellAssay" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="GobletCellOutput" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="BALFSputumAssay" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="BALFSputumOutput" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="LungFunctionAssay" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="LungFunctionOutput" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="FoxJExpressionAssay" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="FoxJExpressionOutput" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="GeneExpressionAssay" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="GeneExpressionOutput" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Container" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1195,36 +1199,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>exposure_agent</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>exposure_concentration</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>exposure_duration</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>timing_post_exposure</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
@@ -1325,6 +1309,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>exposure_agent</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>exposure_concentration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>exposure_duration</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>timing_post_exposure</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1463,7 +1571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1529,7 +1637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1598,7 +1706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1669,7 +1777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1720,7 +1828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1743,270 +1851,6 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>unit</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>analysis_software</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>airway_region</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>informs_on_key_event</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>study_subject</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>has_exposure_condition</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>follows_protocols</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_specified_output</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>assay_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>beat_frequency_hz</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>active_area_percentage</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>cilia_length</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cilia_per_cell</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>percentage_ciliated_cells</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cell_type_ratios</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ciliary_motion_patterns</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ciliary_beat_amplitude</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"coordinated,dyskinetic,immotile,rotational,stiff"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>informs_on_key_event</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>study_subject</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>has_exposure_condition</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>follows_protocols</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>has_specified_output</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>assay_date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>asl_height_um</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>periciliary_layer_depth</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>mucus_layer_thickness</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ion_composition</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>asl_ph</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2085,6 +1929,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>analysis_software</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>airway_region</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>informs_on_key_event</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>study_subject</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>has_exposure_condition</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>follows_protocols</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_specified_output</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>assay_date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>beat_frequency_hz</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>active_area_percentage</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cilia_length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cilia_per_cell</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>percentage_ciliated_cells</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cell_type_ratios</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ciliary_motion_patterns</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ciliary_beat_amplitude</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"coordinated,dyskinetic,immotile,rotational,stiff"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>informs_on_key_event</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>study_subject</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_exposure_condition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>follows_protocols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>has_specified_output</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>assay_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>asl_height_um</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>periciliary_layer_depth</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mucus_layer_thickness</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ion_composition</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>asl_ph</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2145,7 +2253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2206,7 +2314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2272,7 +2380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2393,7 +2501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2464,7 +2572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2515,305 +2623,6 @@
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>normalization_reference</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>phosphorylation_site</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>informs_on_key_event</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>study_subject</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>has_exposure_condition</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>follows_protocols</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_specified_output</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>assay_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>egfr_phosphorylation_y1068</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>egfr_phosphorylation_y1173</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>total_egfr_protein</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>downstream_kinase_activation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>erk_phosphorylation</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>akt_phosphorylation</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pathway_biomarkers</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>egfr_ligand_expression</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>egfr_membrane_localization</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>informs_on_key_event</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>study_subject</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>has_exposure_condition</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>follows_protocols</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>has_specified_output</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>assay_date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>goblet_cell_count</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>goblet_cell_percentage</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>muc5ac_mrna_expression</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>muc5ac_protein_expression</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>muc5b_mrna_expression</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>muc5b_protein_expression</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>muc5ac_muc5b_ratio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mucin_protein_concentration</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mucin_secretion_rate</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>percent_solids</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>goblet_to_ciliated_ratio</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>mucus_viscosity</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2886,6 +2695,305 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>normalization_reference</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>phosphorylation_site</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>informs_on_key_event</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>study_subject</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>has_exposure_condition</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>follows_protocols</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_specified_output</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>assay_date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>egfr_phosphorylation_y1068</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>egfr_phosphorylation_y1173</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>total_egfr_protein</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>downstream_kinase_activation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>erk_phosphorylation</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>akt_phosphorylation</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pathway_biomarkers</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>egfr_ligand_expression</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>egfr_membrane_localization</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>informs_on_key_event</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>study_subject</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_exposure_condition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>follows_protocols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>has_specified_output</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>assay_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>goblet_cell_count</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>goblet_cell_percentage</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>muc5ac_mrna_expression</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>muc5ac_protein_expression</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>muc5b_mrna_expression</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>muc5b_protein_expression</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>muc5ac_muc5b_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mucin_protein_concentration</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mucin_secretion_rate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>percent_solids</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>goblet_to_ciliated_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mucus_viscosity</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2946,7 +3054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3047,7 +3155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3123,7 +3231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3229,7 +3337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3290,7 +3398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3341,7 +3449,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>aopwiki_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>molecular_initiating_event</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>key_events</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>key_event_relationships</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>adverse_outcome</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>stressors</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3417,7 +3586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3463,7 +3632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3541,67 +3710,6 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>protocols</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>aopwiki_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>molecular_initiating_event</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>key_events</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>key_event_relationships</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>adverse_outcome</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>stressors</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>

--- a/artifacts/soma.xlsx
+++ b/artifacts/soma.xlsx
@@ -1,64 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NamedThing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KeyEvent" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="KeyEventRelationship" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AdverseOutcome" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AdverseOutcomePathway" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MolecularInitiatingEvent" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="StudySubject" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ModelSystem" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="InVivoSubject" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="PopulationSubject" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Protocol" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ImagingProtocol" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="StainingProtocol" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SpirometryProtocol" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="MolecularAssayProtocol" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="QuantityValue" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Unit" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="NamedEntity" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CellTypeReference" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="SpeciesReference" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="ChemicalEntityReference" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="AnatomicalEntityReference" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="ExposureCondition" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="CellularSystem" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="CellLine" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="CellCultureConditions" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="CellCultureMedium" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="MediumSupplement" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="QuantityRange" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="CiliaryFunctionAssay" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="CiliaryFunctionOutput" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="ASLAssay" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="ASLOutput" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="MucociliaryClearanceAssay" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="MucociliaryClearanceOutput" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="OxidativeStressAssay" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="OxidativeStressOutput" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="CFTRFunctionAssay" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="CFTRFunctionOutput" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="EGFRSignalingAssay" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="EGFRSignalingOutput" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="GobletCellAssay" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="GobletCellOutput" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="BALFSputumAssay" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="BALFSputumOutput" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="LungFunctionAssay" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="LungFunctionOutput" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="FoxJExpressionAssay" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="FoxJExpressionOutput" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="GeneExpressionAssay" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="GeneExpressionOutput" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="Container" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NamedThing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KeyEvent" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KeyEventRelationship" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AdverseOutcome" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AdverseOutcomePathway" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolecularInitiatingEvent" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StudySubject" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelSystem" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InVivoSubject" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PopulationSubject" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protocol" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ImagingProtocol" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StainingProtocol" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpirometryProtocol" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolecularAssayProtocol" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantityValue" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NamedEntity" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CellTypeReference" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpeciesReference" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalEntityReference" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnatomicalEntityReference" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExposureCondition" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CellularSystem" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CellLine" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CellCultureConditions" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CellCultureMedium" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MediumSupplement" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantityRange" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CiliaryFunctionAssay" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CiliaryFunctionOutput" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASLAssay" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASLOutput" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MucociliaryClearanceAssay" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MucociliaryClearanceOutput" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OxidativeStressAssay" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OxidativeStressOutput" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFTRFunctionAssay" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFTRFunctionOutput" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EGFRSignalingAssay" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EGFRSignalingOutput" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GobletCellAssay" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GobletCellOutput" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALFSputumAssay" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALFSputumOutput" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LungFunctionAssay" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LungFunctionOutput" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FoxJExpressionAssay" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FoxJExpressionOutput" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GeneExpressionAssay" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GeneExpressionOutput" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Container" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
